--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R2" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R3" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129149694</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B2" t="n">
         <v>98659</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R2" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B3" t="n">
         <v>98659</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R3" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R2" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R3" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129149694</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129149694</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R2" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R3" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R2" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R3" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129149694</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129149694</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R2" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R3" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B2" t="n">
         <v>98724</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R2" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B3" t="n">
         <v>98724</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R3" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B2" t="n">
         <v>98727</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R2" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B3" t="n">
         <v>98727</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R3" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40789-2025 artfynd.xlsx
+++ b/artfynd/A 40789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129149080</v>
+        <v>129149065</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469115</v>
+        <v>469108</v>
       </c>
       <c r="R2" t="n">
-        <v>6857895</v>
+        <v>6857892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129149065</v>
+        <v>129149080</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469108</v>
+        <v>469115</v>
       </c>
       <c r="R3" t="n">
-        <v>6857892</v>
+        <v>6857895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129149173</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129149694</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129149113</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
